--- a/products-storage/03-dogovor-podryada/03-kalendarnyy-plan.xlsx
+++ b/products-storage/03-dogovor-podryada/03-kalendarnyy-plan.xlsx
@@ -12,6 +12,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр'!$A$3:$I$103</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Инструкция'!$A$1:$A$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Реестр'!$A$1:$I$106</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Реестр'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -96,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -111,6 +114,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -475,9 +484,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I103"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -498,10 +507,11 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="54" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Заполняйте одну операцию в одной строке. Серые колонки — исходные данные; оранжевые — контроль.</t>
+          <t xml:space="preserve">Приложение № 2 к договору № {{НОМЕР_ДОГОВОРА}} от {{ДАТА_ДОГОВОРА}}.
+Объект: {{ОБЪЕКТ}}. Генподрядчик: {{НАИМЕНОВАНИЕ_ГЕНПОДРЯДЧИКА}}. Субподрядчик: {{НАИМЕНОВАНИЕ_СУБПОДРЯДЧИКА}}.</t>
         </is>
       </c>
     </row>
@@ -1652,13 +1662,46 @@
       <c r="H103" s="4" t="n"/>
       <c r="I103" s="4" t="n"/>
     </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Генподрядчик</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Субподрядчик</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{ДОЛЖНОСТЬ_ФИО_ПОЛНОМОЧИЯ}}
+Подпись __________________
+Дата __________________</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{ДОЛЖНОСТЬ_ФИО_ПОЛНОМОЧИЯ}}
+Подпись __________________
+Дата __________________</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:I103"/>
-  <mergeCells count="2">
+  <mergeCells count="6">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A105:D105"/>
+    <mergeCell ref="E105:I105"/>
+    <mergeCell ref="A106:D106"/>
+    <mergeCell ref="E106:I106"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1666,12 +1709,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1681,14 +1724,16 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="90" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3" ht="100" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>1. Сделайте копию файла для объекта. 2. Назначьте владельца реестра. 3. Обновляйте статусы не реже двух раз в неделю. 4. Не удаляйте историю — меняйте статус и добавляйте комментарий. 5. Храните ссылки на доказательства передачи.</t>
+          <t>Порядок заполнения:
+Внесите даты этапов, передачу фронта и исходных данных, зависимые работы и ответственного. Сверьте события и сроки с договором до подписания приложения.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>